--- a/pregenereated_results/s2/ate_summary_retention_survival.xlsx
+++ b/pregenereated_results/s2/ate_summary_retention_survival.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR2"/>
+  <dimension ref="A1:AS2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,210 +441,215 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Best_Interval</t>
+          <t>Interaction_Type</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Best_HR</t>
+          <t>Headline_HR_Label</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Best_HR_95_CI</t>
+          <t>Hazard_Ratio</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>HR_95_CI</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>P_Value</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Concordance</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>PH_Assumption_Met</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>N_Events_Treated</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>N_Events_Control</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>N_Total</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ESS</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>HR_0_3mo</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>HR_CI_0_3mo</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>P_0_3mo</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Sig_0_3mo</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>HR_3mo_6mo</t>
-        </is>
-      </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>HR_CI_3mo_6mo</t>
+          <t>HR_3_6mo</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>P_3mo_6mo</t>
+          <t>HR_CI_3_6mo</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Sig_3mo_6mo</t>
+          <t>P_3_6mo</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>HR_6mo_9mo</t>
+          <t>Sig_3_6mo</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>HR_CI_6mo_9mo</t>
+          <t>HR_6_9mo</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>P_6mo_9mo</t>
+          <t>HR_CI_6_9mo</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>Sig_6mo_9mo</t>
+          <t>P_6_9mo</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>HR_9mo_12mo</t>
+          <t>Sig_6_9mo</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>HR_CI_9mo_12mo</t>
+          <t>HR_9_12mo</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>P_9mo_12mo</t>
+          <t>HR_CI_9_12mo</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Sig_9mo_12mo</t>
+          <t>P_9_12mo</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
+          <t>Sig_9_12mo</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>Surv_Trained_3mo</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Surv_Control_3mo</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Surv_Diff_3mo</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Surv_Trained_6mo</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Surv_Control_6mo</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Surv_Diff_6mo</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Surv_Trained_9mo</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Surv_Control_9mo</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Surv_Diff_9mo</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>Surv_Trained_12mo</t>
-        </is>
-      </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>Surv_Control_12mo</t>
+          <t>Surv_Trained_365d</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>Surv_Diff_12mo</t>
+          <t>Surv_Control_365d</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
+          <t>Surv_Diff_365d</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
           <t>P_Value_Corrected</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Significant</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Significance</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>Correction_Method</t>
         </is>
@@ -663,136 +668,143 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0–3 mo</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>0.5947</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>[0.395, 0.895]</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>0.01274825851729578</v>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Reference: 0-3mo</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.5868</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>[0.386, 0.892]</t>
+        </is>
       </c>
       <c r="G2" t="n">
-        <v>0.5167</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="n">
+        <v>0.0126</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.664</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
         <v>68</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>1368</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>7220</v>
       </c>
-      <c r="L2" t="n">
-        <v>7094.386718944054</v>
-      </c>
       <c r="M2" t="n">
-        <v>0.5947</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>[0.395, 0.895]</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>0.0127</v>
-      </c>
-      <c r="P2" t="inlineStr">
+        <v>7094.386718944053</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.5868</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>[0.386, 0.892]</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>0.0126</v>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>*</t>
         </is>
       </c>
-      <c r="Q2" t="n">
-        <v>0.8448</v>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>[0.491, 1.454]</t>
-        </is>
-      </c>
-      <c r="S2" t="n">
-        <v>0.5425</v>
-      </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="n">
-        <v>0.8985</v>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>[0.495, 1.632]</t>
-        </is>
-      </c>
-      <c r="W2" t="n">
-        <v>0.7252999999999999</v>
-      </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="n">
-        <v>0.9439</v>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>[0.523, 1.703]</t>
-        </is>
-      </c>
-      <c r="AA2" t="n">
-        <v>0.8479</v>
-      </c>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="n">
+      <c r="R2" t="n">
+        <v>0.8462</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>[0.510, 1.405]</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>0.5183</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="n">
+        <v>0.8958</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>[0.509, 1.576]</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>0.7026</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="n">
+        <v>0.9484</v>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>[0.540, 1.667]</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8539</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="n">
         <v>0.9351</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AE2" t="n">
         <v>0.894</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AF2" t="n">
         <v>0.0411</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AG2" t="n">
         <v>0.9002</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AH2" t="n">
         <v>0.8548</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AI2" t="n">
         <v>0.0454</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AJ2" t="n">
         <v>0.872</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AK2" t="n">
         <v>0.825</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AL2" t="n">
         <v>0.047</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AM2" t="n">
         <v>0.8436</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="AN2" t="n">
         <v>0.7968</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="AO2" t="n">
         <v>0.0469</v>
       </c>
-      <c r="AO2" t="n">
-        <v>0.01274825851729578</v>
-      </c>
-      <c r="AP2" t="b">
+      <c r="AP2" t="n">
+        <v>0.0126</v>
+      </c>
+      <c r="AQ2" t="b">
         <v>1</v>
       </c>
-      <c r="AQ2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>*</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
